--- a/SOF3032/Slide/Template/Template_Schedule_Estimation.xlsx
+++ b/SOF3032/Slide/Template/Template_Schedule_Estimation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FoobAB\Documents\GitHub\CNTT_TH02862\SOF3032\Slide\Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0E433127-BE37-40E0-986C-C757B67C9B2F}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D8A93DD-31D4-400E-A2FF-3733F3661E92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9165" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WBS" sheetId="22" r:id="rId1"/>
@@ -28,7 +28,10 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -990,22 +993,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="B1:K30"/>
-  <sheetFormatPr defaultColWidth="3.85546875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="3.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.28515625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="11.85546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="37.5703125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.28515625" style="1" customWidth="1"/>
-    <col min="6" max="7" width="12.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="11.88671875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="37.5546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" style="1" customWidth="1"/>
+    <col min="6" max="7" width="12.88671875" style="1" customWidth="1"/>
     <col min="8" max="8" width="31" style="1" customWidth="1"/>
     <col min="9" max="9" width="2" style="1" customWidth="1"/>
-    <col min="10" max="10" width="7.28515625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="24.28515625" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="3.85546875" style="1"/>
+    <col min="10" max="10" width="7.33203125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="24.33203125" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="3.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:11" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="12" t="s">
         <v>0</v>
       </c>
@@ -1022,7 +1025,7 @@
       <c r="B2" s="5"/>
       <c r="K2" s="15"/>
     </row>
-    <row r="3" spans="2:11" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:11" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="10"/>
       <c r="C3" s="10" t="s">
         <v>5</v>
@@ -1034,14 +1037,14 @@
       <c r="H3" s="41"/>
       <c r="K3" s="35"/>
     </row>
-    <row r="4" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:11" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
       <c r="H4" s="9"/>
       <c r="J4" s="3"/>
       <c r="K4" s="4"/>
     </row>
-    <row r="5" spans="2:11" s="2" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:11" s="2" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="27" t="s">
         <v>2</v>
       </c>
@@ -1065,7 +1068,7 @@
       </c>
       <c r="K5" s="6"/>
     </row>
-    <row r="6" spans="2:11" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:11" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="24">
         <v>1</v>
       </c>
@@ -1118,7 +1121,7 @@
       <c r="H8" s="39"/>
       <c r="K8" s="8"/>
     </row>
-    <row r="9" spans="2:11" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:11" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="23">
         <v>3</v>
       </c>
@@ -1136,7 +1139,7 @@
       <c r="H9" s="39"/>
       <c r="K9" s="7"/>
     </row>
-    <row r="10" spans="2:11" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:11" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="23">
         <v>3</v>
       </c>
@@ -1154,7 +1157,7 @@
       <c r="H10" s="39"/>
       <c r="K10" s="7"/>
     </row>
-    <row r="11" spans="2:11" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:11" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="23">
         <v>4</v>
       </c>
@@ -1172,7 +1175,7 @@
       <c r="H11" s="39"/>
       <c r="K11" s="7"/>
     </row>
-    <row r="12" spans="2:11" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:11" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="23">
         <v>4</v>
       </c>
@@ -1190,7 +1193,7 @@
       <c r="H12" s="39"/>
       <c r="K12" s="7"/>
     </row>
-    <row r="13" spans="2:11" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:11" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="23">
         <v>4</v>
       </c>
@@ -1208,7 +1211,7 @@
       <c r="H13" s="39"/>
       <c r="K13" s="7"/>
     </row>
-    <row r="14" spans="2:11" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:11" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="23">
         <v>2</v>
       </c>
@@ -1226,7 +1229,7 @@
       <c r="H14" s="39"/>
       <c r="K14" s="7"/>
     </row>
-    <row r="15" spans="2:11" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:11" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="23">
         <v>1</v>
       </c>
@@ -1243,7 +1246,7 @@
       <c r="H15" s="39"/>
       <c r="K15" s="7"/>
     </row>
-    <row r="16" spans="2:11" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:11" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="23">
         <v>2</v>
       </c>
@@ -1261,7 +1264,7 @@
       <c r="H16" s="39"/>
       <c r="K16" s="7"/>
     </row>
-    <row r="17" spans="2:11" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:11" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="23">
         <v>3</v>
       </c>
@@ -1279,7 +1282,7 @@
       <c r="H17" s="39"/>
       <c r="K17" s="7"/>
     </row>
-    <row r="18" spans="2:11" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:11" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="23">
         <v>3</v>
       </c>
@@ -1297,7 +1300,7 @@
       <c r="H18" s="39"/>
       <c r="K18" s="7"/>
     </row>
-    <row r="19" spans="2:11" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:11" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="23">
         <v>1</v>
       </c>
@@ -1314,7 +1317,7 @@
       <c r="H19" s="39"/>
       <c r="K19" s="7"/>
     </row>
-    <row r="20" spans="2:11" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:11" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="23">
         <v>2</v>
       </c>
@@ -1331,7 +1334,7 @@
       <c r="G20" s="36"/>
       <c r="H20" s="39"/>
     </row>
-    <row r="21" spans="2:11" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:11" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="23">
         <v>3</v>
       </c>
@@ -1348,7 +1351,7 @@
       <c r="G21" s="36"/>
       <c r="H21" s="39"/>
     </row>
-    <row r="22" spans="2:11" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:11" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="23">
         <v>4</v>
       </c>
@@ -1365,7 +1368,7 @@
       <c r="G22" s="36"/>
       <c r="H22" s="39"/>
     </row>
-    <row r="23" spans="2:11" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:11" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="23">
         <v>2</v>
       </c>
@@ -1382,7 +1385,7 @@
       <c r="G23" s="36"/>
       <c r="H23" s="39"/>
     </row>
-    <row r="24" spans="2:11" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:11" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="23"/>
       <c r="C24" s="25" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -1394,7 +1397,7 @@
       <c r="G24" s="36"/>
       <c r="H24" s="39"/>
     </row>
-    <row r="25" spans="2:11" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:11" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="23"/>
       <c r="C25" s="25" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -1406,7 +1409,7 @@
       <c r="G25" s="36"/>
       <c r="H25" s="39"/>
     </row>
-    <row r="26" spans="2:11" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:11" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="23"/>
       <c r="C26" s="25" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -1418,7 +1421,7 @@
       <c r="G26" s="36"/>
       <c r="H26" s="39"/>
     </row>
-    <row r="27" spans="2:11" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:11" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="23"/>
       <c r="C27" s="25" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -1430,7 +1433,7 @@
       <c r="G27" s="36"/>
       <c r="H27" s="39"/>
     </row>
-    <row r="28" spans="2:11" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:11" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="23"/>
       <c r="C28" s="25" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -1442,7 +1445,7 @@
       <c r="G28" s="36"/>
       <c r="H28" s="39"/>
     </row>
-    <row r="29" spans="2:11" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:11" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="23"/>
       <c r="C29" s="25" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -1454,7 +1457,7 @@
       <c r="G29" s="36"/>
       <c r="H29" s="39"/>
     </row>
-    <row r="30" spans="2:11" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:11" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="32"/>
       <c r="C30" s="26" t="str">
         <f t="shared" ca="1" si="0"/>
